--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484766_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484766_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2634</v>
+        <v>5.1886</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8392</v>
+        <v>3.6056</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4243</v>
+        <v>1.583</v>
       </c>
       <c r="G2" t="n">
         <v>2.7432</v>
@@ -610,13 +610,13 @@
         <v>2.2644</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8976</v>
+        <v>0.8228</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6307</v>
+        <v>0.3972</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2669</v>
+        <v>0.4257</v>
       </c>
       <c r="V2" t="n">
         <v>1.2452</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V. CARLES TEJEDO</t>
+          <t>A. PINTO MEDINA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5962</v>
+        <v>2.6295</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.7977</v>
+        <v>1.1168</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3939</v>
+        <v>1.5127</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6895</v>
+        <v>-2.358</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.0988</v>
+        <v>1.2404</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4093</v>
+        <v>-3.5984</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.1203</v>
+        <v>-1.9706</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.1614</v>
+        <v>1.8445</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0411</v>
+        <v>-3.8151</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4308</v>
+        <v>-0.3874</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0626</v>
+        <v>-0.6041</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3682</v>
+        <v>0.2167</v>
       </c>
       <c r="P3" t="n">
+        <v>1.3209</v>
+      </c>
+      <c r="Q3" t="n">
         <v>-0.9435</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-2.0757</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.1322</v>
+        <v>2.2644</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0405</v>
+        <v>0.2328</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1488</v>
+        <v>-0.0065</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1893</v>
+        <v>0.2393</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1886</v>
+        <v>3.4338</v>
       </c>
       <c r="W3" t="n">
-        <v>1.547</v>
+        <v>4.0374</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6415999999999999</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. PINTO MEDINA</t>
+          <t>J. ARTIGUES DAÑOBEITIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4473</v>
+        <v>0.9509</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2785</v>
+        <v>0.9509</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1688</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.358</v>
+        <v>0.9509</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2404</v>
+        <v>0.9509</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.5984</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.9706</v>
+        <v>0.9509</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8445</v>
+        <v>0.9509</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.8151</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3874</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6041</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2167</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3209</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2644</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9494</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8448</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1046</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>3.4338</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>4.0374</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. POU CAMPILLO</t>
+          <t>Á. PINTO MEDINA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.06</v>
+        <v>0.9509</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8539</v>
+        <v>0.9509</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7939000000000001</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5951</v>
+        <v>0.9509</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4477</v>
+        <v>0.9509</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1475</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3453</v>
+        <v>0.9509</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2631</v>
+        <v>0.9509</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0823</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7502</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8154</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06519999999999999</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6983</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5213</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1503</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.371</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.8678</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Á. PINTO MEDINA</t>
+          <t>V. CARLES TEJEDO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9509</v>
+        <v>0.8659</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9509</v>
+        <v>-1.9725</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2.8384</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9509</v>
+        <v>-0.6895</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9509</v>
+        <v>-1.0988</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.4093</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9509</v>
+        <v>-1.1203</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9509</v>
+        <v>-1.1614</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.0411</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.4308</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.0626</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.3682</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.1322</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.3103</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.3235</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.6338</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.1886</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.547</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. ARTIGUES DAÑOBEITIA</t>
+          <t>A. POU CAMPILLO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9509</v>
+        <v>-0.1898</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9509</v>
+        <v>1.1332</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-1.323</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9509</v>
+        <v>0.5951</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9509</v>
+        <v>0.4477</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.1475</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9509</v>
+        <v>1.3453</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9509</v>
+        <v>1.2631</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.0823</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-0.7502</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.8154</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.6983</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.2715</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.4296</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.8419</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.8678</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-3.113</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4078</v>
+        <v>-0.3284</v>
       </c>
       <c r="E8" t="n">
         <v>-0.0165</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3913</v>
+        <v>-0.3119</v>
       </c>
       <c r="G8" t="n">
         <v>-0.272</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1358</v>
+        <v>-0.0564</v>
       </c>
       <c r="T8" t="n">
         <v>-0.0588</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.077</v>
+        <v>0.0024</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.919</v>
+        <v>-1.3739</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4945</v>
+        <v>-1.9229</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5754</v>
+        <v>0.549</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0118</v>
@@ -1156,13 +1156,13 @@
         <v>1.3209</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0928</v>
+        <v>0.6379</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7824</v>
+        <v>0.354</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3104</v>
+        <v>0.284</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2452</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. SUCH LOPEZ</t>
+          <t>C. SANCHEZ VIDAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0716</v>
+        <v>-1.9432</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.4946</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1316</v>
+        <v>-1.4485</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5231</v>
+        <v>-1.0338</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5642</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0411</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0623</v>
+        <v>-0.3709</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0211</v>
+        <v>-0.4532</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0411</v>
+        <v>0.0823</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5854</v>
+        <v>-0.6629</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5854</v>
+        <v>-0.4899</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0.173</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7548</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9435</v>
+        <v>-2.0757</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1887</v>
+        <v>2.0757</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1711</v>
+        <v>0.6566</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0588</v>
+        <v>0.405</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1123</v>
+        <v>0.2517</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6226</v>
+        <v>-1.566</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.547</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6226</v>
+        <v>-3.113</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. SANCHEZ VIDAL</t>
+          <t>A. SUCH LOPEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3123</v>
+        <v>-1.9477</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9431</v>
+        <v>-0.8426</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3692</v>
+        <v>-1.1051</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0338</v>
+        <v>-0.5231</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9429999999999999</v>
+        <v>-0.5642</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.09080000000000001</v>
+        <v>0.0411</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3709</v>
+        <v>0.0623</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4532</v>
+        <v>0.0211</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0823</v>
+        <v>0.0411</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6629</v>
+        <v>-0.5854</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4899</v>
+        <v>-0.5854</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.173</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0757</v>
+        <v>-0.9435</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0757</v>
+        <v>0.1887</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2875</v>
+        <v>-0.0472</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0436</v>
+        <v>0.0386</v>
       </c>
       <c r="U11" t="n">
-        <v>0.331</v>
+        <v>-0.0858</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.566</v>
+        <v>-0.6226</v>
       </c>
       <c r="W11" t="n">
-        <v>1.547</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.113</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9496</v>
+        <v>-3.0236</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5271</v>
+        <v>-3.7863</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5775</v>
+        <v>0.7627</v>
       </c>
       <c r="G12" t="n">
         <v>-0.0226</v>
@@ -1390,13 +1390,13 @@
         <v>1.5096</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8324</v>
+        <v>0.0936</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.823</v>
+        <v>-0.0822</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0094</v>
+        <v>0.1758</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6415999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.6972</v>
+        <v>-4.2802</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.8396</v>
+        <v>-5.8195</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1425</v>
+        <v>1.5393</v>
       </c>
       <c r="G13" t="n">
         <v>0.3986</v>
@@ -1468,13 +1468,13 @@
         <v>1.6983</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0388</v>
+        <v>0.3781</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.0575</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0388</v>
+        <v>0.4356</v>
       </c>
       <c r="V13" t="n">
         <v>0.038</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.0888</v>
+        <v>-2.500999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.685099999999999</v>
+        <v>-7.0975</v>
       </c>
       <c r="F14" t="n">
-        <v>4.596400000000001</v>
+        <v>4.5966</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7278999999999999</v>
+        <v>0.7278999999999998</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3777</v>
+        <v>1.377699999999999</v>
       </c>
       <c r="I14" t="n">
         <v>-0.6497000000000001</v>
@@ -1546,22 +1546,22 @@
         <v>14.1525</v>
       </c>
       <c r="S14" t="n">
-        <v>3.712199999999999</v>
+        <v>4.3</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5079000000000001</v>
+        <v>1.0959</v>
       </c>
       <c r="U14" t="n">
-        <v>3.2041</v>
+        <v>3.204400000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9624000000000006</v>
+        <v>0.9624000000000001</v>
       </c>
       <c r="W14" t="n">
         <v>9.8856</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.923300000000001</v>
+        <v>-8.923299999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.654</v>
+        <v>6.9904</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7934</v>
+        <v>4.4755</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8606</v>
+        <v>2.5149</v>
       </c>
       <c r="G15" t="n">
         <v>2.6943</v>
@@ -1624,13 +1624,13 @@
         <v>4.1514</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.1345</v>
+        <v>-0.7982</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.3274</v>
+        <v>-0.6454</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8070000000000001</v>
+        <v>-0.1528</v>
       </c>
       <c r="V15" t="n">
         <v>2.4524</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2513</v>
+        <v>2.2128</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1153</v>
+        <v>0.9204</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1361</v>
+        <v>1.2924</v>
       </c>
       <c r="G16" t="n">
         <v>2.8327</v>
@@ -1702,13 +1702,13 @@
         <v>2.6418</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2422</v>
+        <v>-0.2807</v>
       </c>
       <c r="T16" t="n">
-        <v>0.074</v>
+        <v>-0.1208</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3162</v>
+        <v>-0.1598</v>
       </c>
       <c r="V16" t="n">
         <v>-1.8488</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9285</v>
+        <v>1.8923</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8171</v>
+        <v>0.2325</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1113</v>
+        <v>1.6598</v>
       </c>
       <c r="G17" t="n">
         <v>1.5258</v>
@@ -1780,13 +1780,13 @@
         <v>2.0757</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5914</v>
+        <v>0.5552</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6771</v>
+        <v>0.0925</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0858</v>
+        <v>0.4627</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4124</v>
+        <v>1.6927</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1786</v>
+        <v>-1.0811</v>
       </c>
       <c r="F18" t="n">
-        <v>2.591</v>
+        <v>2.7738</v>
       </c>
       <c r="G18" t="n">
         <v>-0.279</v>
@@ -1858,13 +1858,13 @@
         <v>1.6983</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6484</v>
+        <v>-0.3681</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7055</v>
+        <v>-0.608</v>
       </c>
       <c r="U18" t="n">
-        <v>0.057</v>
+        <v>0.2399</v>
       </c>
       <c r="V18" t="n">
         <v>0.6415999999999999</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>W. LADSON BUGALLO</t>
+          <t>O. KOVAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2293</v>
+        <v>0.0721</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6459</v>
+        <v>-0.991</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8752</v>
+        <v>1.0631</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1527</v>
+        <v>-0.6686</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.324</v>
+        <v>-1.8117</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4767</v>
+        <v>1.1431</v>
       </c>
       <c r="J19" t="n">
-        <v>1.069</v>
+        <v>0.5296</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3286</v>
+        <v>-0.7865</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7403</v>
+        <v>1.3162</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0837</v>
+        <v>-1.1982</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6526</v>
+        <v>-1.0252</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7363</v>
+        <v>-0.173</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.1322</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.3401</v>
+        <v>-1.1322</v>
       </c>
       <c r="R19" t="n">
-        <v>4.3401</v>
+        <v>2.2644</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9823</v>
+        <v>-0.7123</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2047</v>
+        <v>-0.3885</v>
       </c>
       <c r="U19" t="n">
-        <v>1.187</v>
+        <v>-0.3239</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.9058</v>
+        <v>0.3208</v>
       </c>
       <c r="W19" t="n">
-        <v>1.8298</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.7356</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. KOVAL</t>
+          <t>J. MAS MICO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.1992</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8935999999999999</v>
+        <v>-0.3393</v>
       </c>
       <c r="F20" t="n">
-        <v>0.825</v>
+        <v>0.1401</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6686</v>
+        <v>0.1334</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8117</v>
+        <v>0.9149</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1431</v>
+        <v>-0.7815</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5296</v>
+        <v>0.4535</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7865</v>
+        <v>1.062</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3162</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1982</v>
+        <v>-0.3202</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0252</v>
+        <v>-0.1471</v>
       </c>
       <c r="O20" t="n">
         <v>-0.173</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1322</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.1322</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2644</v>
+        <v>1.1322</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.853</v>
+        <v>-0.3326</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.291</v>
+        <v>-0.2832</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.0493</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3208</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3208</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MAS MICO</t>
+          <t>W. LADSON BUGALLO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7272</v>
+        <v>-0.3347</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6316000000000001</v>
+        <v>-1.9383</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0956</v>
+        <v>1.6036</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1334</v>
+        <v>1.1527</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9149</v>
+        <v>-0.324</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7815</v>
+        <v>1.4767</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4535</v>
+        <v>1.069</v>
       </c>
       <c r="K21" t="n">
-        <v>1.062</v>
+        <v>0.3286</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6084000000000001</v>
+        <v>0.7403</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3202</v>
+        <v>0.0837</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1471</v>
+        <v>-0.6526</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.173</v>
+        <v>0.7363</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1322</v>
+        <v>-4.3401</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1322</v>
+        <v>4.3401</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8606</v>
+        <v>0.4184</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5755</v>
+        <v>-0.497</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2851</v>
+        <v>0.9154</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.9058</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6226</v>
+        <v>1.8298</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6226</v>
+        <v>-3.7356</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6957</v>
+        <v>-2.9026</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2473</v>
+        <v>-1.637</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4485</v>
+        <v>-1.2656</v>
       </c>
       <c r="G22" t="n">
         <v>-3.2603</v>
@@ -2170,13 +2170,13 @@
         <v>1.6983</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1681</v>
+        <v>-0.0388</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1357</v>
+        <v>-0.254</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0324</v>
+        <v>0.2152</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9244</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.895</v>
+        <v>-4.3861</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.7253</v>
+        <v>-4.2381</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1698</v>
+        <v>-0.148</v>
       </c>
       <c r="G23" t="n">
         <v>-4.8589</v>
@@ -2248,13 +2248,13 @@
         <v>2.6418</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7154</v>
+        <v>-0.2065</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9871</v>
+        <v>-0.4999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2717</v>
+        <v>0.2934</v>
       </c>
       <c r="V23" t="n">
         <v>0.3018</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>3.089000000000002</v>
+        <v>5.0377</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.596500000000001</v>
+        <v>-4.5964</v>
       </c>
       <c r="F24" t="n">
-        <v>7.6853</v>
+        <v>9.6341</v>
       </c>
       <c r="G24" t="n">
         <v>-0.7279</v>
@@ -2326,16 +2326,16 @@
         <v>22.644</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.7123</v>
+        <v>-1.7636</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.2044</v>
+        <v>-3.2043</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.508</v>
+        <v>1.4408</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.9623999999999999</v>
+        <v>-0.9624000000000004</v>
       </c>
       <c r="W24" t="n">
         <v>8.923299999999999</v>
